--- a/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274422830117951</v>
+        <v>1.251155409527301</v>
       </c>
       <c r="C3" t="n">
-        <v>4.646736457218754</v>
+        <v>4.653638143579609</v>
       </c>
       <c r="D3" t="n">
-        <v>6.077200006547682</v>
+        <v>6.058213005947548</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99835929388439</v>
+        <v>11.96300655905446</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.438857213388069</v>
+        <v>1.364819870254728</v>
       </c>
       <c r="C4" t="n">
-        <v>5.16503329484831</v>
+        <v>5.180066171308311</v>
       </c>
       <c r="D4" t="n">
-        <v>6.302893941158359</v>
+        <v>6.31685510747992</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90678444939474</v>
+        <v>12.86174114904296</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.657738545401708</v>
+        <v>1.525129768513422</v>
       </c>
       <c r="C5" t="n">
-        <v>5.816995866572605</v>
+        <v>5.837257369827095</v>
       </c>
       <c r="D5" t="n">
-        <v>6.608005549985518</v>
+        <v>6.59369493592674</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08273996195983</v>
+        <v>13.95608207426726</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.910849363645307</v>
+        <v>1.704360752212402</v>
       </c>
       <c r="C6" t="n">
-        <v>6.585900921007028</v>
+        <v>6.622312772922366</v>
       </c>
       <c r="D6" t="n">
-        <v>6.888085517545347</v>
+        <v>6.896090675764992</v>
       </c>
       <c r="E6" t="n">
-        <v>15.38483580219768</v>
+        <v>15.22276420089976</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.190556857208279</v>
+        <v>1.905112671337232</v>
       </c>
       <c r="C7" t="n">
-        <v>7.473213417427834</v>
+        <v>7.538141290201573</v>
       </c>
       <c r="D7" t="n">
-        <v>7.305483410662957</v>
+        <v>7.225262674457426</v>
       </c>
       <c r="E7" t="n">
-        <v>16.96925368529907</v>
+        <v>16.66851663599623</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.381279522926681</v>
+        <v>1.132891163517929</v>
       </c>
       <c r="C8" t="n">
-        <v>5.056147037707485</v>
+        <v>5.212621312595211</v>
       </c>
       <c r="D8" t="n">
-        <v>5.542877446753307</v>
+        <v>5.476809745494125</v>
       </c>
       <c r="E8" t="n">
-        <v>11.98030400738747</v>
+        <v>11.82232222160727</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.736480847867876</v>
+        <v>1.400497058378394</v>
       </c>
       <c r="C9" t="n">
-        <v>6.144728690861801</v>
+        <v>6.448023316157543</v>
       </c>
       <c r="D9" t="n">
-        <v>6.062921521763727</v>
+        <v>6.043363011856947</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9441310604934</v>
+        <v>13.89188338639288</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.124072071690082</v>
+        <v>1.677961785012068</v>
       </c>
       <c r="C10" t="n">
-        <v>7.358356631400024</v>
+        <v>7.845770956901275</v>
       </c>
       <c r="D10" t="n">
-        <v>6.613482580846115</v>
+        <v>6.574340102649654</v>
       </c>
       <c r="E10" t="n">
-        <v>16.09591128393622</v>
+        <v>16.098072844563</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.528192551368008</v>
+        <v>1.962801099167291</v>
       </c>
       <c r="C11" t="n">
-        <v>8.715477674490618</v>
+        <v>9.349241392645121</v>
       </c>
       <c r="D11" t="n">
-        <v>7.129045175073217</v>
+        <v>7.070199064167906</v>
       </c>
       <c r="E11" t="n">
-        <v>18.37271540093184</v>
+        <v>18.38224155598032</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.952092904994504</v>
+        <v>2.251750868256312</v>
       </c>
       <c r="C12" t="n">
-        <v>10.14967046496816</v>
+        <v>11.02258197419006</v>
       </c>
       <c r="D12" t="n">
-        <v>7.72662984577171</v>
+        <v>7.595645279738937</v>
       </c>
       <c r="E12" t="n">
-        <v>20.82839321573437</v>
+        <v>20.86997812218531</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.362951157673364</v>
+        <v>2.528863554387167</v>
       </c>
       <c r="C13" t="n">
-        <v>11.60462692327787</v>
+        <v>12.78113272299226</v>
       </c>
       <c r="D13" t="n">
-        <v>8.230167622058056</v>
+        <v>8.053989646602778</v>
       </c>
       <c r="E13" t="n">
-        <v>23.19774570300929</v>
+        <v>23.3639859239822</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.947738357840459</v>
+        <v>1.467732452803067</v>
       </c>
       <c r="C14" t="n">
-        <v>8.20484844599525</v>
+        <v>9.032363585904887</v>
       </c>
       <c r="D14" t="n">
-        <v>6.291078558721731</v>
+        <v>6.144591983771065</v>
       </c>
       <c r="E14" t="n">
-        <v>16.44366536255744</v>
+        <v>16.64468802247902</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.018159120666083</v>
+        <v>1.485305736709084</v>
       </c>
       <c r="C15" t="n">
-        <v>8.772396793820333</v>
+        <v>9.908622499330377</v>
       </c>
       <c r="D15" t="n">
-        <v>6.355167048854963</v>
+        <v>6.157099449523169</v>
       </c>
       <c r="E15" t="n">
-        <v>17.14572296334138</v>
+        <v>17.55102768556263</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.372520954513969</v>
+        <v>1.703057377511027</v>
       </c>
       <c r="C16" t="n">
-        <v>10.26674442688553</v>
+        <v>11.86291893183521</v>
       </c>
       <c r="D16" t="n">
-        <v>6.915205026742555</v>
+        <v>6.647011188896412</v>
       </c>
       <c r="E16" t="n">
-        <v>19.55447040814205</v>
+        <v>20.21298749824264</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.920121794919997</v>
+        <v>1.352229835398429</v>
       </c>
       <c r="C17" t="n">
-        <v>9.364331754618904</v>
+        <v>11.07693171981521</v>
       </c>
       <c r="D17" t="n">
-        <v>6.459114495780615</v>
+        <v>6.17194347481138</v>
       </c>
       <c r="E17" t="n">
-        <v>17.74356804531952</v>
+        <v>18.60110503002502</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.209452660838574</v>
+        <v>1.528365191017349</v>
       </c>
       <c r="C18" t="n">
-        <v>10.87788237277917</v>
+        <v>13.01794510588158</v>
       </c>
       <c r="D18" t="n">
-        <v>6.979588041187061</v>
+        <v>6.561216257022283</v>
       </c>
       <c r="E18" t="n">
-        <v>20.0669230748048</v>
+        <v>21.10752655392121</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.231276912303981</v>
+        <v>1.518459356681499</v>
       </c>
       <c r="C19" t="n">
-        <v>11.59129879450124</v>
+        <v>13.98632140639655</v>
       </c>
       <c r="D19" t="n">
-        <v>7.143696987428958</v>
+        <v>6.639481184004838</v>
       </c>
       <c r="E19" t="n">
-        <v>20.96627269423418</v>
+        <v>22.14426194708288</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.510476141914732</v>
+        <v>1.671317474232727</v>
       </c>
       <c r="C20" t="n">
-        <v>13.27664544342766</v>
+        <v>16.08339340752999</v>
       </c>
       <c r="D20" t="n">
-        <v>7.622092826231386</v>
+        <v>7.08761955856238</v>
       </c>
       <c r="E20" t="n">
-        <v>23.40921441157377</v>
+        <v>24.8423304403251</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.505569009324739</v>
+        <v>0.9866368078139596</v>
       </c>
       <c r="C21" t="n">
-        <v>9.751218889908488</v>
+        <v>11.79963547481946</v>
       </c>
       <c r="D21" t="n">
-        <v>6.405736873100716</v>
+        <v>5.913596566438832</v>
       </c>
       <c r="E21" t="n">
-        <v>17.66252477233394</v>
+        <v>18.69986884907225</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251155409527301</v>
+        <v>1.251096504665046</v>
       </c>
       <c r="C3" t="n">
-        <v>4.653638143579609</v>
+        <v>4.649298818726839</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058213005947548</v>
+        <v>6.084494391990235</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96300655905446</v>
+        <v>11.98488971538212</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.364819870254728</v>
+        <v>1.369616858937148</v>
       </c>
       <c r="C4" t="n">
-        <v>5.180066171308311</v>
+        <v>5.205483582229468</v>
       </c>
       <c r="D4" t="n">
-        <v>6.31685510747992</v>
+        <v>6.319848995908303</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86174114904296</v>
+        <v>12.89494943707492</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.525129768513422</v>
+        <v>1.531441600839515</v>
       </c>
       <c r="C5" t="n">
-        <v>5.837257369827095</v>
+        <v>5.922737782758054</v>
       </c>
       <c r="D5" t="n">
-        <v>6.59369493592674</v>
+        <v>6.65863531016493</v>
       </c>
       <c r="E5" t="n">
-        <v>13.95608207426726</v>
+        <v>14.1128146937625</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.704360752212402</v>
+        <v>1.720311140662649</v>
       </c>
       <c r="C6" t="n">
-        <v>6.622312772922366</v>
+        <v>6.81193467832395</v>
       </c>
       <c r="D6" t="n">
-        <v>6.896090675764992</v>
+        <v>7.066459100794343</v>
       </c>
       <c r="E6" t="n">
-        <v>15.22276420089976</v>
+        <v>15.59870491978094</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.905112671337232</v>
+        <v>1.928278506188178</v>
       </c>
       <c r="C7" t="n">
-        <v>7.538141290201573</v>
+        <v>7.812760152957309</v>
       </c>
       <c r="D7" t="n">
-        <v>7.225262674457426</v>
+        <v>7.437297918476307</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66851663599623</v>
+        <v>17.17833657762179</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.132891163517929</v>
+        <v>1.153461845545817</v>
       </c>
       <c r="C8" t="n">
-        <v>5.212621312595211</v>
+        <v>5.406875355823734</v>
       </c>
       <c r="D8" t="n">
-        <v>5.476809745494125</v>
+        <v>5.619178153880505</v>
       </c>
       <c r="E8" t="n">
-        <v>11.82232222160727</v>
+        <v>12.17951535525006</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.400497058378394</v>
+        <v>1.43720249922954</v>
       </c>
       <c r="C9" t="n">
-        <v>6.448023316157543</v>
+        <v>6.58532342850366</v>
       </c>
       <c r="D9" t="n">
-        <v>6.043363011856947</v>
+        <v>6.12591112498066</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89188338639288</v>
+        <v>14.14843705271386</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.677961785012068</v>
+        <v>1.729545486268911</v>
       </c>
       <c r="C10" t="n">
-        <v>7.845770956901275</v>
+        <v>7.87077577131179</v>
       </c>
       <c r="D10" t="n">
-        <v>6.574340102649654</v>
+        <v>6.62861863189249</v>
       </c>
       <c r="E10" t="n">
-        <v>16.098072844563</v>
+        <v>16.22893988947319</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.962801099167291</v>
+        <v>2.030069554450619</v>
       </c>
       <c r="C11" t="n">
-        <v>9.349241392645121</v>
+        <v>9.256658724683062</v>
       </c>
       <c r="D11" t="n">
-        <v>7.070199064167906</v>
+        <v>7.081711271514837</v>
       </c>
       <c r="E11" t="n">
-        <v>18.38224155598032</v>
+        <v>18.36843955064852</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.251750868256312</v>
+        <v>2.334696401916995</v>
       </c>
       <c r="C12" t="n">
-        <v>11.02258197419006</v>
+        <v>10.80133174799222</v>
       </c>
       <c r="D12" t="n">
-        <v>7.595645279738937</v>
+        <v>7.510237406932378</v>
       </c>
       <c r="E12" t="n">
-        <v>20.86997812218531</v>
+        <v>20.64626555684159</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.528863554387167</v>
+        <v>2.6286508499529</v>
       </c>
       <c r="C13" t="n">
-        <v>12.78113272299226</v>
+        <v>12.47200782785073</v>
       </c>
       <c r="D13" t="n">
-        <v>8.053989646602778</v>
+        <v>7.961286374776875</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3639859239822</v>
+        <v>23.06194505258051</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.467732452803067</v>
+        <v>1.520128327778719</v>
       </c>
       <c r="C14" t="n">
-        <v>9.032363585904887</v>
+        <v>8.927787820448517</v>
       </c>
       <c r="D14" t="n">
-        <v>6.144591983771065</v>
+        <v>6.032280046405229</v>
       </c>
       <c r="E14" t="n">
-        <v>16.64468802247902</v>
+        <v>16.48019619463246</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.485305736709084</v>
+        <v>1.542620167683013</v>
       </c>
       <c r="C15" t="n">
-        <v>9.908622499330377</v>
+        <v>9.725929069047089</v>
       </c>
       <c r="D15" t="n">
-        <v>6.157099449523169</v>
+        <v>6.025692519309733</v>
       </c>
       <c r="E15" t="n">
-        <v>17.55102768556263</v>
+        <v>17.29424175603983</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.703057377511027</v>
+        <v>1.779250816837622</v>
       </c>
       <c r="C16" t="n">
-        <v>11.86291893183521</v>
+        <v>11.59638424760924</v>
       </c>
       <c r="D16" t="n">
-        <v>6.647011188896412</v>
+        <v>6.442719309119693</v>
       </c>
       <c r="E16" t="n">
-        <v>20.21298749824264</v>
+        <v>19.81835437356656</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.352229835398429</v>
+        <v>1.420107871670054</v>
       </c>
       <c r="C17" t="n">
-        <v>11.07693171981521</v>
+        <v>10.75320041433982</v>
       </c>
       <c r="D17" t="n">
-        <v>6.17194347481138</v>
+        <v>5.944600158938948</v>
       </c>
       <c r="E17" t="n">
-        <v>18.60110503002502</v>
+        <v>18.11790844494882</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.528365191017349</v>
+        <v>1.607621683181194</v>
       </c>
       <c r="C18" t="n">
-        <v>13.01794510588158</v>
+        <v>12.61754912218156</v>
       </c>
       <c r="D18" t="n">
-        <v>6.561216257022283</v>
+        <v>6.340195396365199</v>
       </c>
       <c r="E18" t="n">
-        <v>21.10752655392121</v>
+        <v>20.56536620172795</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.518459356681499</v>
+        <v>1.600651274481042</v>
       </c>
       <c r="C19" t="n">
-        <v>13.98632140639655</v>
+        <v>13.54362191412053</v>
       </c>
       <c r="D19" t="n">
-        <v>6.639481184004838</v>
+        <v>6.412147685609448</v>
       </c>
       <c r="E19" t="n">
-        <v>22.14426194708288</v>
+        <v>21.55642087421102</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.671317474232727</v>
+        <v>1.770797969104057</v>
       </c>
       <c r="C20" t="n">
-        <v>16.08339340752999</v>
+        <v>15.60176761878059</v>
       </c>
       <c r="D20" t="n">
-        <v>7.08761955856238</v>
+        <v>6.814183187975559</v>
       </c>
       <c r="E20" t="n">
-        <v>24.8423304403251</v>
+        <v>24.18674877586021</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9866368078139596</v>
+        <v>1.047092831441478</v>
       </c>
       <c r="C21" t="n">
-        <v>11.79963547481946</v>
+        <v>11.5011547202973</v>
       </c>
       <c r="D21" t="n">
-        <v>5.913596566438832</v>
+        <v>5.664330824330567</v>
       </c>
       <c r="E21" t="n">
-        <v>18.69986884907225</v>
+        <v>18.21257837606935</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_70_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251096504665046</v>
+        <v>2.590517554125503</v>
       </c>
       <c r="C3" t="n">
-        <v>4.649298818726839</v>
+        <v>7.661978404811439</v>
       </c>
       <c r="D3" t="n">
-        <v>6.084494391990235</v>
+        <v>8.169581873516128</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98488971538212</v>
+        <v>18.42207783245307</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.369616858937148</v>
+        <v>1.061631115301356</v>
       </c>
       <c r="C4" t="n">
-        <v>5.205483582229468</v>
+        <v>4.432820628301553</v>
       </c>
       <c r="D4" t="n">
-        <v>6.319848995908303</v>
+        <v>5.74471688754343</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89494943707492</v>
+        <v>11.23916863114634</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.531441600839515</v>
+        <v>1.145760593980783</v>
       </c>
       <c r="C5" t="n">
-        <v>5.922737782758054</v>
+        <v>5.045471635057599</v>
       </c>
       <c r="D5" t="n">
-        <v>6.65863531016493</v>
+        <v>5.999524572209711</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1128146937625</v>
+        <v>12.19075680124809</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.720311140662649</v>
+        <v>1.247039976453877</v>
       </c>
       <c r="C6" t="n">
-        <v>6.81193467832395</v>
+        <v>5.890833976225161</v>
       </c>
       <c r="D6" t="n">
-        <v>7.066459100794343</v>
+        <v>6.244586994535198</v>
       </c>
       <c r="E6" t="n">
-        <v>15.59870491978094</v>
+        <v>13.38246094721424</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.928278506188178</v>
+        <v>1.354846878067333</v>
       </c>
       <c r="C7" t="n">
-        <v>7.812760152957309</v>
+        <v>6.965948141485321</v>
       </c>
       <c r="D7" t="n">
-        <v>7.437297918476307</v>
+        <v>6.551855178525964</v>
       </c>
       <c r="E7" t="n">
-        <v>17.17833657762179</v>
+        <v>14.87265019807862</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.153461845545817</v>
+        <v>1.457646712420596</v>
       </c>
       <c r="C8" t="n">
-        <v>5.406875355823734</v>
+        <v>8.22019255610638</v>
       </c>
       <c r="D8" t="n">
-        <v>5.619178153880505</v>
+        <v>6.909230294097249</v>
       </c>
       <c r="E8" t="n">
-        <v>12.17951535525006</v>
+        <v>16.58706956262423</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.43720249922954</v>
+        <v>1.555141906859086</v>
       </c>
       <c r="C9" t="n">
-        <v>6.58532342850366</v>
+        <v>9.626227359517586</v>
       </c>
       <c r="D9" t="n">
-        <v>6.12591112498066</v>
+        <v>7.335040888114354</v>
       </c>
       <c r="E9" t="n">
-        <v>14.14843705271386</v>
+        <v>18.51641015449103</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.729545486268911</v>
+        <v>0.9801769079200154</v>
       </c>
       <c r="C10" t="n">
-        <v>7.87077577131179</v>
+        <v>7.068288946265761</v>
       </c>
       <c r="D10" t="n">
-        <v>6.62861863189249</v>
+        <v>5.771851832899678</v>
       </c>
       <c r="E10" t="n">
-        <v>16.22893988947319</v>
+        <v>13.82031768708545</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.030069554450619</v>
+        <v>0.8930271642140262</v>
       </c>
       <c r="C11" t="n">
-        <v>9.256658724683062</v>
+        <v>7.638929799359219</v>
       </c>
       <c r="D11" t="n">
-        <v>7.081711271514837</v>
+        <v>5.617501458837994</v>
       </c>
       <c r="E11" t="n">
-        <v>18.36843955064852</v>
+        <v>14.14945842241124</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.334696401916995</v>
+        <v>0.9400234268163211</v>
       </c>
       <c r="C12" t="n">
-        <v>10.80133174799222</v>
+        <v>9.158478895992433</v>
       </c>
       <c r="D12" t="n">
-        <v>7.510237406932378</v>
+        <v>6.024691136651401</v>
       </c>
       <c r="E12" t="n">
-        <v>20.64626555684159</v>
+        <v>16.12319345946015</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.6286508499529</v>
+        <v>0.727651763433651</v>
       </c>
       <c r="C13" t="n">
-        <v>12.47200782785073</v>
+        <v>8.852821565752231</v>
       </c>
       <c r="D13" t="n">
-        <v>7.961286374776875</v>
+        <v>5.501331252994468</v>
       </c>
       <c r="E13" t="n">
-        <v>23.06194505258051</v>
+        <v>15.08180458218035</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.520128327778719</v>
+        <v>0.7729888724157687</v>
       </c>
       <c r="C14" t="n">
-        <v>8.927787820448517</v>
+        <v>10.50369905278254</v>
       </c>
       <c r="D14" t="n">
-        <v>6.032280046405229</v>
+        <v>5.86354706847633</v>
       </c>
       <c r="E14" t="n">
-        <v>16.48019619463246</v>
+        <v>17.14023499367464</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.542620167683013</v>
+        <v>0.7380877415297945</v>
       </c>
       <c r="C15" t="n">
-        <v>9.725929069047089</v>
+        <v>11.46227751120913</v>
       </c>
       <c r="D15" t="n">
-        <v>6.025692519309733</v>
+        <v>5.917621732026244</v>
       </c>
       <c r="E15" t="n">
-        <v>17.29424175603983</v>
+        <v>18.11798698476516</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.779250816837622</v>
+        <v>0.7975227475448965</v>
       </c>
       <c r="C16" t="n">
-        <v>11.59638424760924</v>
+        <v>13.50628604892803</v>
       </c>
       <c r="D16" t="n">
-        <v>6.442719309119693</v>
+        <v>6.30925070872734</v>
       </c>
       <c r="E16" t="n">
-        <v>19.81835437356656</v>
+        <v>20.61305950520027</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.420107871670054</v>
+        <v>0.4832162200302801</v>
       </c>
       <c r="C17" t="n">
-        <v>10.75320041433982</v>
+        <v>10.18465068385641</v>
       </c>
       <c r="D17" t="n">
-        <v>5.944600158938948</v>
+        <v>5.244005362234337</v>
       </c>
       <c r="E17" t="n">
-        <v>18.11790844494882</v>
+        <v>15.91187226612103</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.607621683181194</v>
+        <v>0.3679786745057895</v>
       </c>
       <c r="C18" t="n">
-        <v>12.61754912218156</v>
+        <v>9.287539449192717</v>
       </c>
       <c r="D18" t="n">
-        <v>6.340195396365199</v>
+        <v>4.776654185104686</v>
       </c>
       <c r="E18" t="n">
-        <v>20.56536620172795</v>
+        <v>14.43217230880319</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.600651274481042</v>
+        <v>0.4292888186360028</v>
       </c>
       <c r="C19" t="n">
-        <v>13.54362191412053</v>
+        <v>11.63723476958295</v>
       </c>
       <c r="D19" t="n">
-        <v>6.412147685609448</v>
+        <v>5.212383268680549</v>
       </c>
       <c r="E19" t="n">
-        <v>21.55642087421102</v>
+        <v>17.2789068568995</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.770797969104057</v>
+        <v>0.486446169977252</v>
       </c>
       <c r="C20" t="n">
-        <v>15.60176761878059</v>
+        <v>14.17980424394951</v>
       </c>
       <c r="D20" t="n">
-        <v>6.814183187975559</v>
+        <v>5.644489703227739</v>
       </c>
       <c r="E20" t="n">
-        <v>24.18674877586021</v>
+        <v>20.3107401171545</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.047092831441478</v>
+        <v>0.5331184558371453</v>
       </c>
       <c r="C21" t="n">
-        <v>11.5011547202973</v>
+        <v>16.79202871793238</v>
       </c>
       <c r="D21" t="n">
-        <v>5.664330824330567</v>
+        <v>6.09672196571199</v>
       </c>
       <c r="E21" t="n">
-        <v>18.21257837606935</v>
+        <v>23.42186913948152</v>
       </c>
     </row>
   </sheetData>
